--- a/templates/TemplateCNPTempExtract.xlsx
+++ b/templates/TemplateCNPTempExtract.xlsx
@@ -3,59 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Extraction Temp" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Production" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Template" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="8Sf5rvJXIUV2NDeT9rfs/2Kg44srN5gc2yAD6T78dq4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="t/rqNlpazDmLgjx/Ysj0FUT6DMWkyry33x5Tce31Lbo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment authorId="0" ref="G50">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB182837g
-LECHAUGUETTE Eric    (2026-03-16 09:35:22)
-LECHAUGUETTE Eric:</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="I49">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB182836c
-LECHAUGUETTE Eric    (2026-03-16 09:35:22)
-LECHAUGUETTE Eric:</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="G49">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB18KCkOg
-LECHAUGUETTE Eric    (2026-03-16 09:35:22)
-LECHAUGUETTE Eric:</t>
-      </text>
-    </comment>
-  </commentList>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mi94k1dEouVs+GNfx1iEv6qbI3tlg=="/>
-    </ext>
-  </extLst>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
   <si>
     <t>AM</t>
   </si>
@@ -156,24 +118,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Fenetres ouvertes </t>
-  </si>
-  <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>T° 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T° </t>
-  </si>
-  <si>
-    <t>Occupation :  20 °C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total </t>
-  </si>
-  <si>
     <t xml:space="preserve">Paramétrage mode hiver </t>
   </si>
   <si>
@@ -187,6 +131,90 @@
   </si>
   <si>
     <t>;</t>
+  </si>
+  <si>
+    <t>{{AM_PM}}</t>
+  </si>
+  <si>
+    <t>{{date_day}}</t>
+  </si>
+  <si>
+    <t>{{date_hour}}</t>
+  </si>
+  <si>
+    <t>T°: {{EXT_TEMP}}°c</t>
+  </si>
+  <si>
+    <t>HYGR: {{EXT_HYGR}}</t>
+  </si>
+  <si>
+    <t>{{MAX_A}}</t>
+  </si>
+  <si>
+    <t>{{MAX_B}}</t>
+  </si>
+  <si>
+    <t>{{MAX_C}}</t>
+  </si>
+  <si>
+    <t>{{MAX_D}}</t>
+  </si>
+  <si>
+    <t>{{AVG_A}}</t>
+  </si>
+  <si>
+    <t>{{AVG_B}}</t>
+  </si>
+  <si>
+    <t>{{AVG_C}}</t>
+  </si>
+  <si>
+    <t>{{AVG_D}}</t>
+  </si>
+  <si>
+    <t>{{MIN_A}}</t>
+  </si>
+  <si>
+    <t>{{MIN_B}}</t>
+  </si>
+  <si>
+    <t>{{MIN_C}}</t>
+  </si>
+  <si>
+    <t>{{MIN_D}}</t>
+  </si>
+  <si>
+    <t>ICV 1R Jeanne Barret</t>
+  </si>
+  <si>
+    <t>{{ICV_1R_Jeanne_Barret}}</t>
+  </si>
+  <si>
+    <t>ICV 1R Studio TV</t>
+  </si>
+  <si>
+    <t>{{ICV_1R_Studio_TV}}</t>
+  </si>
+  <si>
+    <t>ICV  1R06 Commandant Charcot</t>
+  </si>
+  <si>
+    <t>{{ICV_1R06_Commandant_Charcot}}</t>
+  </si>
+  <si>
+    <t>ICV 4R Espace COMEX</t>
+  </si>
+  <si>
+    <t>{{ICV_4R_Espace_COMEX}}</t>
+  </si>
+  <si>
+    <t>{{ICV_4R12._COMEX}}</t>
+  </si>
+  <si>
+    <t>ICV 7R12 Salle du conseil</t>
+  </si>
+  <si>
+    <t>{{ICV_7R12_Salle_du_conseil}}</t>
   </si>
 </sst>
 </file>
@@ -197,7 +225,7 @@
     <numFmt numFmtId="164" formatCode="D/M/YYYY"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -234,41 +262,13 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="16.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16.0"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="16.0"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <u/>
       <sz val="14.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,30 +325,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8D08D"/>
-        <bgColor rgb="FFA8D08D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="35">
     <border/>
     <border>
       <left style="medium">
@@ -716,79 +698,6 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
@@ -802,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="81">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -888,9 +797,6 @@
     <xf borderId="23" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="23" fillId="5" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
@@ -949,79 +855,47 @@
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="33" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="16" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
+    <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="12" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="16" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="16" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="24" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="29" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="16" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="36" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="38" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="39" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="40" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="31" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="23" fillId="12" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="19" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="23" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="13" fillId="13" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="13" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="16" fillId="13" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="16" fillId="13" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="16" fillId="13" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="41" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="42" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="32" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="27" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1036,14 +910,47 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4733925" cy="1323975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4733925" cy="1323975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1610,7 +1517,7 @@
       <c r="I13" s="23">
         <v>22.0</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="32" t="s">
         <v>11</v>
       </c>
       <c r="K13" s="19">
@@ -1649,13 +1556,13 @@
       <c r="X13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="Y13" s="40">
+      <c r="Y13" s="39">
         <v>20.0</v>
       </c>
       <c r="Z13" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="AA13" s="40">
+      <c r="AA13" s="39">
         <v>19.1</v>
       </c>
       <c r="AB13" s="32" t="s">
@@ -1670,15 +1577,15 @@
       <c r="AE13" s="34">
         <v>19.8</v>
       </c>
-      <c r="AG13" s="41" t="s">
+      <c r="AG13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="AH13" s="42" t="s">
+      <c r="AH13" s="41" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="42" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="30" t="s">
@@ -1723,7 +1630,7 @@
       <c r="Q14" s="19">
         <v>21.0</v>
       </c>
-      <c r="R14" s="39" t="s">
+      <c r="R14" s="32" t="s">
         <v>10</v>
       </c>
       <c r="S14" s="19">
@@ -1762,10 +1669,10 @@
       <c r="AE14" s="34">
         <v>19.6</v>
       </c>
-      <c r="AG14" s="41" t="s">
+      <c r="AG14" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AH14" s="44"/>
+      <c r="AH14" s="43"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="10"/>
@@ -1850,10 +1757,10 @@
       <c r="AE15" s="34">
         <v>19.5</v>
       </c>
-      <c r="AG15" s="41" t="s">
+      <c r="AG15" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AH15" s="44">
+      <c r="AH15" s="43">
         <v>21.5</v>
       </c>
     </row>
@@ -1919,13 +1826,13 @@
       <c r="X16" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="Y16" s="45">
+      <c r="Y16" s="44">
         <v>19.3</v>
       </c>
       <c r="Z16" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="AA16" s="45">
+      <c r="AA16" s="44">
         <v>19.6</v>
       </c>
       <c r="AB16" s="32" t="s">
@@ -1940,154 +1847,154 @@
       <c r="AE16" s="34">
         <v>19.2</v>
       </c>
-      <c r="AG16" s="41" t="s">
+      <c r="AG16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="AH16" s="42">
+      <c r="AH16" s="41">
         <v>20.9</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="10"/>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <v>23.8</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="47">
         <v>21.5</v>
       </c>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="47">
         <v>21.6</v>
       </c>
-      <c r="J17" s="49" t="s">
+      <c r="J17" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="46" t="s">
+      <c r="M17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="N17" s="47" t="s">
+      <c r="N17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="48">
+      <c r="O17" s="47">
         <v>20.5</v>
       </c>
-      <c r="P17" s="49" t="s">
+      <c r="P17" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="48">
+      <c r="Q17" s="47">
         <v>20.8</v>
       </c>
-      <c r="R17" s="49" t="s">
+      <c r="R17" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="S17" s="48">
+      <c r="S17" s="47">
         <v>20.3</v>
       </c>
-      <c r="T17" s="49" t="s">
+      <c r="T17" s="48" t="s">
         <v>11</v>
       </c>
       <c r="U17" s="25">
         <v>0.0</v>
       </c>
-      <c r="W17" s="46" t="s">
+      <c r="W17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="X17" s="47" t="s">
+      <c r="X17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="50">
         <v>18.0</v>
       </c>
-      <c r="Z17" s="49" t="s">
+      <c r="Z17" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="50">
         <v>20.0</v>
       </c>
-      <c r="AB17" s="49" t="s">
+      <c r="AB17" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="AC17" s="52">
+      <c r="AC17" s="51">
         <v>19.7</v>
       </c>
-      <c r="AD17" s="49" t="s">
+      <c r="AD17" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="AE17" s="53" t="s">
+      <c r="AE17" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="AG17" s="54" t="s">
+      <c r="AG17" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="AH17" s="55">
+      <c r="AH17" s="54">
         <v>20.5</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="10"/>
-      <c r="C18" s="56"/>
-      <c r="E18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="U18" s="57"/>
-      <c r="W18" s="56"/>
-      <c r="Y18" s="57"/>
-      <c r="AA18" s="57"/>
-      <c r="AC18" s="57"/>
-      <c r="AE18" s="57"/>
+      <c r="C18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="U18" s="56"/>
+      <c r="W18" s="55"/>
+      <c r="Y18" s="56"/>
+      <c r="AA18" s="56"/>
+      <c r="AC18" s="56"/>
+      <c r="AE18" s="56"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="AA19" s="57"/>
-      <c r="AG19" s="60"/>
-      <c r="AH19" s="60"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="AA19" s="56"/>
+      <c r="AG19" s="59"/>
+      <c r="AH19" s="59"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="60" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
-      <c r="Y20" s="57"/>
-      <c r="AA20" s="62"/>
-      <c r="AF20" s="63" t="s">
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="Y20" s="56"/>
+      <c r="AA20" s="61"/>
+      <c r="AF20" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="AG20" s="63"/>
-      <c r="AH20" s="63"/>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -2095,1247 +2002,205 @@
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="65"/>
+      <c r="A22" s="64"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="65"/>
+      <c r="A23" s="64"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="65"/>
-      <c r="C24" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="68"/>
+      <c r="A24" s="64"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="65"/>
-      <c r="C25" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="71"/>
-      <c r="J25" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="70"/>
+      <c r="A25" s="64"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="65"/>
-      <c r="C26" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="72"/>
-      <c r="J26" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="71"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="66"/>
     </row>
     <row r="27" ht="20.25" customHeight="1">
-      <c r="A27" s="65"/>
-      <c r="C27" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" s="72"/>
-      <c r="J27" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="72"/>
+      <c r="A27" s="10"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="65"/>
-      <c r="C28" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" s="70"/>
-      <c r="J28" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K28" s="70"/>
+      <c r="A28" s="10"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="C29" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="73"/>
-      <c r="J29" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K29" s="70"/>
+      <c r="A29" s="67" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="65"/>
-      <c r="C30" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="73"/>
-      <c r="J30" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K30" s="70"/>
+      <c r="A30" s="68" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="65"/>
-      <c r="C31" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31" s="70"/>
-      <c r="J31" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K31" s="70"/>
+      <c r="A31" s="68" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" ht="29.25" customHeight="1">
-      <c r="A32" s="10"/>
+      <c r="A32" s="68" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="10"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="76"/>
-      <c r="N34" s="76"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="76"/>
-      <c r="Q34" s="76"/>
-      <c r="R34" s="76"/>
-      <c r="S34" s="76"/>
-      <c r="T34" s="76"/>
-      <c r="U34" s="76"/>
-      <c r="V34" s="76"/>
-      <c r="W34" s="76"/>
-      <c r="X34" s="76"/>
-      <c r="Y34" s="76"/>
-      <c r="Z34" s="76"/>
-      <c r="AA34" s="76"/>
-      <c r="AB34" s="76"/>
-      <c r="AC34" s="76"/>
-      <c r="AD34" s="76"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
+      <c r="A34" s="10"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="3">
-        <v>46050.0</v>
-      </c>
-      <c r="B35" s="77"/>
+      <c r="A35" s="10"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="D36" s="78"/>
+      <c r="A36" s="10"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="A37" s="10"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="8"/>
+      <c r="A38" s="10"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12"/>
-      <c r="Q39" s="12"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
-      <c r="U39" s="13"/>
-      <c r="W39" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="12"/>
-      <c r="AE39" s="13"/>
+      <c r="A39" s="10"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="10"/>
-      <c r="C40" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="24">
-        <v>23.8</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="19">
-        <v>25.1</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="17">
-        <v>23.5</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="K40" s="19">
-        <v>25.2</v>
-      </c>
-      <c r="L40" s="20"/>
-      <c r="M40" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="N40" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="O40" s="19">
-        <v>21.7</v>
-      </c>
-      <c r="P40" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q40" s="19">
-        <v>22.3</v>
-      </c>
-      <c r="R40" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="S40" s="19">
-        <v>21.8</v>
-      </c>
-      <c r="T40" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="U40" s="19">
-        <v>24.0</v>
-      </c>
-      <c r="W40" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="X40" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y40" s="24">
-        <v>20.9</v>
-      </c>
-      <c r="Z40" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA40" s="24">
-        <v>19.7</v>
-      </c>
-      <c r="AB40" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC40" s="17">
-        <v>21.1</v>
-      </c>
-      <c r="AD40" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE40" s="79">
-        <v>21.5</v>
-      </c>
-      <c r="AG40" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH40" s="81"/>
+      <c r="T40" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="C41" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="33">
-        <v>23.9</v>
-      </c>
-      <c r="F41" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="23">
-        <v>23.1</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="23">
-        <v>22.3</v>
-      </c>
-      <c r="J41" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K41" s="19">
-        <v>23.5</v>
-      </c>
-      <c r="M41" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="N41" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="23">
-        <v>21.4</v>
-      </c>
-      <c r="P41" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q41" s="23">
-        <v>21.7</v>
-      </c>
-      <c r="R41" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S41" s="23">
-        <v>21.2</v>
-      </c>
-      <c r="T41" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U41" s="19">
-        <v>21.8</v>
-      </c>
-      <c r="W41" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="X41" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y41" s="33">
-        <v>20.1</v>
-      </c>
-      <c r="Z41" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA41" s="33">
-        <v>20.1</v>
-      </c>
-      <c r="AB41" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC41" s="19">
-        <v>19.9</v>
-      </c>
-      <c r="AD41" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE41" s="34">
-        <v>21.0</v>
-      </c>
-      <c r="AG41" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH41" s="36" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="40">
-        <v>23.7</v>
-      </c>
-      <c r="F42" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="23">
-        <v>22.6</v>
-      </c>
-      <c r="H42" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="23">
-        <v>22.8</v>
-      </c>
-      <c r="J42" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K42" s="19">
-        <v>22.9</v>
-      </c>
-      <c r="M42" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="N42" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O42" s="23">
-        <v>21.7</v>
-      </c>
-      <c r="P42" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q42" s="23">
-        <v>21.8</v>
-      </c>
-      <c r="R42" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" s="23">
-        <v>21.5</v>
-      </c>
-      <c r="T42" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U42" s="19">
-        <v>21.7</v>
-      </c>
-      <c r="W42" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="X42" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y42" s="40">
-        <v>21.0</v>
-      </c>
-      <c r="Z42" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA42" s="40">
-        <v>20.6</v>
-      </c>
-      <c r="AB42" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC42" s="19">
-        <v>20.4</v>
-      </c>
-      <c r="AD42" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE42" s="34">
-        <v>20.5</v>
-      </c>
-      <c r="AG42" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH42" s="42" t="s">
-        <v>15</v>
-      </c>
+      <c r="A42" s="10"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="33">
-        <v>23.2</v>
-      </c>
-      <c r="F43" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="23">
-        <v>23.1</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="23">
-        <v>22.6</v>
-      </c>
-      <c r="J43" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K43" s="19">
-        <v>23.1</v>
-      </c>
-      <c r="M43" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="23">
-        <v>21.6</v>
-      </c>
-      <c r="P43" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q43" s="23">
-        <v>22.0</v>
-      </c>
-      <c r="R43" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S43" s="23">
-        <v>21.8</v>
-      </c>
-      <c r="T43" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U43" s="19">
-        <v>21.8</v>
-      </c>
-      <c r="W43" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="X43" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y43" s="33">
-        <v>21.0</v>
-      </c>
-      <c r="Z43" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA43" s="33">
-        <v>21.4</v>
-      </c>
-      <c r="AB43" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC43" s="19">
-        <v>21.1</v>
-      </c>
-      <c r="AD43" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE43" s="34">
-        <v>20.5</v>
-      </c>
-      <c r="AG43" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH43" s="44">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="23">
-        <v>22.7</v>
-      </c>
-      <c r="F44" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="23">
-        <v>23.0</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44" s="23">
-        <v>23.0</v>
-      </c>
-      <c r="J44" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K44" s="19">
-        <v>22.8</v>
-      </c>
-      <c r="M44" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O44" s="23">
-        <v>21.5</v>
-      </c>
-      <c r="P44" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q44" s="23">
-        <v>21.6</v>
-      </c>
-      <c r="R44" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S44" s="23">
-        <v>21.6</v>
-      </c>
-      <c r="T44" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U44" s="19">
-        <v>21.6</v>
-      </c>
-      <c r="W44" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="X44" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y44" s="23">
-        <v>20.5</v>
-      </c>
-      <c r="Z44" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA44" s="23">
-        <v>20.0</v>
-      </c>
-      <c r="AB44" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC44" s="19">
-        <v>21.0</v>
-      </c>
-      <c r="AD44" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE44" s="34">
-        <v>20.7</v>
-      </c>
-      <c r="AG44" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH44" s="44">
-        <v>22.4</v>
-      </c>
-    </row>
+      <c r="A43" s="65"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="66"/>
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="66"/>
+      <c r="Y43" s="66"/>
+      <c r="Z43" s="66"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="66"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="66"/>
+      <c r="AE43" s="66"/>
+      <c r="AF43" s="66"/>
+      <c r="AG43" s="66"/>
+      <c r="AH43" s="66"/>
+    </row>
+    <row r="44" ht="14.25" customHeight="1"/>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="C45" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="45">
-        <v>22.2</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="23">
-        <v>22.9</v>
-      </c>
-      <c r="H45" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I45" s="45">
-        <v>22.3</v>
-      </c>
-      <c r="J45" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K45" s="19">
-        <v>23.1</v>
-      </c>
-      <c r="M45" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="N45" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="19">
-        <v>21.2</v>
-      </c>
-      <c r="P45" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q45" s="19">
-        <v>21.3</v>
-      </c>
-      <c r="R45" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S45" s="19">
-        <v>21.8</v>
-      </c>
-      <c r="T45" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U45" s="19">
-        <v>21.3</v>
-      </c>
-      <c r="W45" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="X45" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="45">
-        <v>20.2</v>
-      </c>
-      <c r="Z45" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA45" s="45">
-        <v>20.0</v>
-      </c>
-      <c r="AB45" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC45" s="19">
-        <v>21.3</v>
-      </c>
-      <c r="AD45" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE45" s="34">
-        <v>20.4</v>
-      </c>
-      <c r="AG45" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH45" s="42">
-        <v>21.4</v>
-      </c>
+      <c r="A45" s="64"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="C46" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="51">
-        <v>24.5</v>
-      </c>
-      <c r="F46" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="48">
-        <v>22.9</v>
-      </c>
-      <c r="H46" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" s="48">
-        <v>23.0</v>
-      </c>
-      <c r="J46" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="K46" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="48">
-        <v>21.8</v>
-      </c>
-      <c r="P46" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q46" s="48">
-        <v>21.5</v>
-      </c>
-      <c r="R46" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="S46" s="48">
-        <v>21.7</v>
-      </c>
-      <c r="T46" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="U46" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="W46" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="X46" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y46" s="51">
-        <v>20.4</v>
-      </c>
-      <c r="Z46" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA46" s="51">
-        <v>20.9</v>
-      </c>
-      <c r="AB46" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC46" s="52">
-        <v>21.2</v>
-      </c>
-      <c r="AD46" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE46" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG46" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH46" s="55">
-        <v>22.9</v>
-      </c>
+      <c r="A46" s="64"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="Z47" s="83"/>
+      <c r="A47" s="64"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="C48" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="85" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC48" s="86"/>
+      <c r="A48" s="64"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="10"/>
-      <c r="C49" s="87" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="88"/>
-      <c r="F49" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49" s="89"/>
-      <c r="H49" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="I49" s="89"/>
-      <c r="J49" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="K49" s="90"/>
-      <c r="AF49" s="63" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG49" s="63"/>
-      <c r="AH49" s="63"/>
+      <c r="A49" s="64"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="10"/>
-      <c r="C50" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="70"/>
-      <c r="F50" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="91"/>
-      <c r="H50" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I50" s="71"/>
-      <c r="J50" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K50" s="71"/>
-      <c r="AF50" s="63"/>
-      <c r="AG50" s="63"/>
-      <c r="AH50" s="63"/>
+      <c r="A50" s="64"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="C51" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="70"/>
-      <c r="F51" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" s="70"/>
-      <c r="H51" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I51" s="70"/>
-      <c r="J51" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K51" s="70"/>
-      <c r="AF51" s="63"/>
-      <c r="AG51" s="63"/>
-      <c r="AH51" s="63"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="C52" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="D52" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="70"/>
-      <c r="F52" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="74"/>
-      <c r="H52" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I52" s="91"/>
-      <c r="J52" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K52" s="91"/>
-      <c r="O52" s="7" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="10"/>
-      <c r="C53" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="70"/>
-      <c r="F53" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" s="92"/>
-      <c r="H53" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I53" s="73"/>
-      <c r="J53" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K53" s="93"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="10"/>
-      <c r="C54" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="93"/>
-      <c r="F54" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G54" s="74"/>
-      <c r="H54" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I54" s="73"/>
-      <c r="J54" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K54" s="93"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="10"/>
-      <c r="C55" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="93"/>
-      <c r="F55" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="92"/>
-      <c r="H55" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I55" s="91"/>
-      <c r="J55" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K55" s="70"/>
-      <c r="AF55" s="63" t="s">
+      <c r="AF55" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="AG55" s="63"/>
-      <c r="AH55" s="63"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="94"/>
-      <c r="B56" s="95"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="95"/>
-      <c r="M56" s="95"/>
-      <c r="N56" s="95"/>
-      <c r="O56" s="95"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="95"/>
-      <c r="R56" s="95"/>
-      <c r="S56" s="95"/>
-      <c r="T56" s="95"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="95"/>
-      <c r="W56" s="95"/>
-      <c r="X56" s="95"/>
-      <c r="Y56" s="95"/>
-      <c r="Z56" s="95"/>
-      <c r="AA56" s="95"/>
-      <c r="AB56" s="95"/>
-      <c r="AC56" s="95"/>
-      <c r="AD56" s="95"/>
-      <c r="AE56" s="95"/>
-      <c r="AF56" s="95"/>
-      <c r="AG56" s="95"/>
-      <c r="AH56" s="95"/>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="10"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="10"/>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="96" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="97" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="97" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="97" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="10"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="10"/>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="10"/>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="10"/>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="10"/>
-    </row>
-    <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="10"/>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="10"/>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="10"/>
-      <c r="T70" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="10"/>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="10"/>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="94"/>
-      <c r="B73" s="95"/>
-      <c r="C73" s="95"/>
-      <c r="D73" s="95"/>
-      <c r="E73" s="95"/>
-      <c r="F73" s="95"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="95"/>
-      <c r="K73" s="95"/>
-      <c r="L73" s="95"/>
-      <c r="M73" s="95"/>
-      <c r="N73" s="95"/>
-      <c r="O73" s="95"/>
-      <c r="P73" s="95"/>
-      <c r="Q73" s="95"/>
-      <c r="R73" s="95"/>
-      <c r="S73" s="95"/>
-      <c r="T73" s="95"/>
-      <c r="U73" s="95"/>
-      <c r="V73" s="95"/>
-      <c r="W73" s="95"/>
-      <c r="X73" s="95"/>
-      <c r="Y73" s="95"/>
-      <c r="Z73" s="95"/>
-      <c r="AA73" s="95"/>
-      <c r="AB73" s="95"/>
-      <c r="AC73" s="95"/>
-      <c r="AD73" s="95"/>
-      <c r="AE73" s="95"/>
-      <c r="AF73" s="95"/>
-      <c r="AG73" s="95"/>
-      <c r="AH73" s="95"/>
-    </row>
+      <c r="AG55" s="62"/>
+      <c r="AH55" s="62"/>
+    </row>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
     <row r="74" ht="14.25" customHeight="1"/>
     <row r="75" ht="14.25" customHeight="1"/>
     <row r="76" ht="14.25" customHeight="1"/>
@@ -4264,22 +3129,1850 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="M39:U39"/>
-    <mergeCell ref="W39:AE39"/>
-    <mergeCell ref="C48:K48"/>
+  <mergeCells count="4">
     <mergeCell ref="A4:AH4"/>
     <mergeCell ref="C10:K10"/>
     <mergeCell ref="M10:U10"/>
     <mergeCell ref="W10:AE10"/>
-    <mergeCell ref="C24:K24"/>
-    <mergeCell ref="A34:AH34"/>
-    <mergeCell ref="C39:K39"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.57"/>
+    <col customWidth="1" min="2" max="2" width="10.71"/>
+    <col customWidth="1" min="3" max="3" width="5.71"/>
+    <col customWidth="1" min="4" max="4" width="3.14"/>
+    <col customWidth="1" min="5" max="5" width="5.29"/>
+    <col customWidth="1" min="6" max="6" width="4.43"/>
+    <col customWidth="1" min="7" max="7" width="5.0"/>
+    <col customWidth="1" min="8" max="8" width="4.14"/>
+    <col customWidth="1" min="9" max="9" width="5.0"/>
+    <col customWidth="1" min="10" max="10" width="4.29"/>
+    <col customWidth="1" min="11" max="11" width="5.43"/>
+    <col customWidth="1" min="12" max="12" width="10.71"/>
+    <col customWidth="1" min="13" max="13" width="5.29"/>
+    <col customWidth="1" min="14" max="14" width="3.71"/>
+    <col customWidth="1" min="15" max="15" width="5.43"/>
+    <col customWidth="1" min="16" max="16" width="3.71"/>
+    <col customWidth="1" min="17" max="17" width="6.71"/>
+    <col customWidth="1" min="18" max="18" width="4.57"/>
+    <col customWidth="1" min="19" max="19" width="5.71"/>
+    <col customWidth="1" min="20" max="20" width="3.71"/>
+    <col customWidth="1" min="21" max="21" width="6.14"/>
+    <col customWidth="1" min="22" max="22" width="10.71"/>
+    <col customWidth="1" min="23" max="23" width="4.29"/>
+    <col customWidth="1" min="24" max="24" width="4.14"/>
+    <col customWidth="1" min="25" max="25" width="5.43"/>
+    <col customWidth="1" min="26" max="26" width="4.43"/>
+    <col customWidth="1" min="27" max="27" width="4.71"/>
+    <col customWidth="1" min="28" max="28" width="4.0"/>
+    <col customWidth="1" min="29" max="29" width="5.14"/>
+    <col customWidth="1" min="30" max="30" width="3.71"/>
+    <col customWidth="1" min="31" max="31" width="5.29"/>
+    <col customWidth="1" min="32" max="32" width="3.29"/>
+    <col customWidth="1" min="33" max="33" width="35.14"/>
+    <col customWidth="1" min="34" max="34" width="7.43"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1"/>
+    <row r="2" ht="14.25" customHeight="1"/>
+    <row r="3" ht="14.25" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="70" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="71" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="8"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="70" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="10"/>
+      <c r="C10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="13"/>
+      <c r="W10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="13"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="10"/>
+      <c r="C11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="R11" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="T11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="U11" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="W11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="X11" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z11" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB11" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE11" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG11" s="27"/>
+      <c r="AH11" s="28"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="74"/>
+      <c r="F12" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="74"/>
+      <c r="H12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="74"/>
+      <c r="J12" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="74"/>
+      <c r="M12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="74"/>
+      <c r="P12" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="74"/>
+      <c r="T12" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="U12" s="74"/>
+      <c r="W12" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="X12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="74"/>
+      <c r="Z12" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="74"/>
+      <c r="AB12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="74"/>
+      <c r="AG12" s="75" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH12" s="76" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="74"/>
+      <c r="F13" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="74"/>
+      <c r="H13" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="74"/>
+      <c r="J13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="74"/>
+      <c r="M13" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="74"/>
+      <c r="P13" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" s="74"/>
+      <c r="T13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="U13" s="74"/>
+      <c r="W13" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="X13" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE13" s="74"/>
+      <c r="AG13" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH13" s="76" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="74"/>
+      <c r="F14" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="74"/>
+      <c r="H14" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="74"/>
+      <c r="J14" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="74"/>
+      <c r="M14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="74"/>
+      <c r="P14" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="74"/>
+      <c r="T14" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="U14" s="74"/>
+      <c r="W14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="X14" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="74"/>
+      <c r="AB14" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE14" s="74"/>
+      <c r="AG14" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH14" s="76" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="10"/>
+      <c r="C15" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="74"/>
+      <c r="F15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="74"/>
+      <c r="H15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="74"/>
+      <c r="J15" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="74"/>
+      <c r="M15" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="74"/>
+      <c r="P15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="74"/>
+      <c r="T15" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="U15" s="74"/>
+      <c r="W15" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="X15" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="74"/>
+      <c r="Z15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="74"/>
+      <c r="AB15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE15" s="74"/>
+      <c r="AG15" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH15" s="76" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="10"/>
+      <c r="C16" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="74"/>
+      <c r="F16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="74"/>
+      <c r="H16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="74"/>
+      <c r="J16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="74"/>
+      <c r="M16" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="74"/>
+      <c r="P16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" s="74"/>
+      <c r="T16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="U16" s="74"/>
+      <c r="W16" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="X16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE16" s="74"/>
+      <c r="AG16" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH16" s="76" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="10"/>
+      <c r="C17" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="78"/>
+      <c r="F17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="78"/>
+      <c r="H17" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="78"/>
+      <c r="J17" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="78"/>
+      <c r="M17" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="78"/>
+      <c r="P17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" s="78"/>
+      <c r="T17" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="U17" s="78"/>
+      <c r="W17" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="X17" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="78"/>
+      <c r="Z17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="78"/>
+      <c r="AB17" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="78"/>
+      <c r="AD17" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE17" s="78"/>
+      <c r="AG17" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH17" s="80" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="10"/>
+      <c r="C18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="U18" s="56"/>
+      <c r="W18" s="55"/>
+      <c r="Y18" s="56"/>
+      <c r="AA18" s="56"/>
+      <c r="AC18" s="56"/>
+      <c r="AE18" s="56"/>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="AA19" s="56"/>
+      <c r="AG19" s="59"/>
+      <c r="AH19" s="59"/>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="Y20" s="56"/>
+      <c r="AA20" s="61"/>
+      <c r="AF20" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="64"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="64"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="64"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="64"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="65"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="66"/>
+    </row>
+    <row r="27" ht="20.25" customHeight="1">
+      <c r="A27" s="10"/>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="10"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="67" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="68" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" ht="29.25" customHeight="1">
+      <c r="A32" s="68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" ht="27.75" customHeight="1">
+      <c r="A33" s="10"/>
+    </row>
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="10"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="10"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="10"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="10"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="10"/>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="10"/>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="10"/>
+      <c r="T40" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="10"/>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="10"/>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="65"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="66"/>
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="66"/>
+      <c r="Y43" s="66"/>
+      <c r="Z43" s="66"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="66"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="66"/>
+      <c r="AE43" s="66"/>
+      <c r="AF43" s="66"/>
+      <c r="AG43" s="66"/>
+      <c r="AH43" s="66"/>
+    </row>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="64"/>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="64"/>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="64"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="A48" s="64"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="A49" s="64"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="A50" s="64"/>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
+      <c r="A51" s="10"/>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
+      <c r="A52" s="10"/>
+    </row>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" s="10"/>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="A54" s="10"/>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="10"/>
+      <c r="AF55" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG55" s="62"/>
+      <c r="AH55" s="62"/>
+    </row>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A4:AH4"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="W10:AE10"/>
+    <mergeCell ref="M10:U10"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>